--- a/dist/SUBMISSION_FINAL/P5_China_IJOEM/p5_china_ijoem_replication_data.xlsx
+++ b/dist/SUBMISSION_FINAL/P5_China_IJOEM/p5_china_ijoem_replication_data.xlsx
@@ -12,6 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_Regression_Coefficients" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_Turning_Points" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_Robustness" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_Figures_Embedded" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -21,7 +22,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -48,6 +49,25 @@
     <font>
       <b val="1"/>
       <i val="1"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00305496"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="00666666"/>
+      <sz val="9"/>
     </font>
   </fonts>
   <fills count="4">
@@ -80,7 +100,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -91,6 +111,12 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -165,6 +191,111 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>5</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5715000" cy="3733800"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>37</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5715000" cy="2981325"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId2"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>63</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5715000" cy="3305175"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId3"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>92</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5715000" cy="2571750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId4"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -590,7 +721,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
@@ -1457,7 +1587,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
@@ -6344,7 +6473,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
@@ -6441,10 +6569,6 @@
       <c r="E5" t="n">
         <v>-1.34404661020249</v>
       </c>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -6464,10 +6588,6 @@
       <c r="E6" t="n">
         <v>-1.24985089171598</v>
       </c>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6555,8 +6675,6 @@
           <t>2700</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
           <t>Private firms only; 148 state-owned excluded by file design</t>
@@ -6584,8 +6702,6 @@
           <t>1708</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
           <t>Optional; manuscript v1.2 does NOT apply this filter</t>
@@ -6613,8 +6729,6 @@
           <t>(no N change)</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
           <t>Verify with codebook recode summary</t>
@@ -6851,8 +6965,6 @@
           <t>1187</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
           <t>Optional; manuscript v1.2 does NOT apply this filter</t>
@@ -6880,8 +6992,6 @@
           <t>(no N change)</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
           <t>2024 separates -9 (DK) from -8 (refuse)</t>
@@ -6987,7 +7097,6 @@
           <t>exact</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -7018,7 +7127,6 @@
           <t>exact</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -7049,7 +7157,6 @@
           <t>exact</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -7115,7 +7222,6 @@
           <t>within 2</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -7146,7 +7252,6 @@
           <t>within 2</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -7212,7 +7317,6 @@
           <t>off 26</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -7260,10 +7364,6 @@
           <t>Discrepancy &gt; +/- 10 firms vs N_expected</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr"/>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr"/>
-      <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
           <t>Trigger root-cause review</t>
@@ -7281,10 +7381,6 @@
           <t>Mfg filter: 2012 may use 15-37 strict (no 38) in v1.2</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr"/>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
           <t>Check methods section</t>
@@ -7302,10 +7398,6 @@
           <t>2024 mfg filter: a4a vs d1a2_v4 discrepancy</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr"/>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
           <t>d1a2_v4 reflects realized industry; a4a reflects frame</t>
@@ -7323,10 +7415,6 @@
           <t>Composite missing rule (&gt;=3/4 vs &gt;=2/4 for TCI)</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr"/>
-      <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
           <t>Cross-check v1.2 footnote (likely cause of 26-firm gap)</t>
@@ -7344,10 +7432,6 @@
           <t>foreigndummy threshold (b2b &gt; 0 vs b2b &gt;= 10)</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr"/>
-      <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr"/>
-      <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
           <t>Check methods</t>
@@ -7357,4 +7441,111 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H92"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="8" t="inlineStr">
+        <is>
+          <t>P5_China_IJOEM — Embedded Figures (data-driven, source-traceable)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="40" customHeight="1">
+      <c r="A2" s="9" t="inlineStr">
+        <is>
+          <t>Each figure below was rendered from a CSV / data file produced by the paper's Stata or R replication pipeline. Provenance is listed under each figure. See 'STATA_REPLICATION_GUIDE.md' (Vietnamese + English) for end-to-end reproduction instructions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="10" t="inlineStr">
+        <is>
+          <t>Figure 1: figure_1_conceptual_model.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="11" t="inlineStr">
+        <is>
+          <t>Provenance: scripts/render_conceptual_models.py → matplotlib (theoretical diagram, not data-driven)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="10" t="inlineStr">
+        <is>
+          <t>Figure 2: figure_2_turning_points.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="11" t="inlineStr">
+        <is>
+          <t>Provenance: p5/replication/figures/ ← p5/replication/turning_points.csv (Stata delta-method CI)</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="10" t="inlineStr">
+        <is>
+          <t>Figure 3: figure_3_predicted_curves.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="11" t="inlineStr">
+        <is>
+          <t>Provenance: p5/replication/figures/ ← p5/replication/predicted_by_wave.csv (Stata margins, atmeans)</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="10" t="inlineStr">
+        <is>
+          <t>Figure 4: figure_4_level_shifts.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="11" t="inlineStr">
+        <is>
+          <t>Provenance: p5/replication/figures/ ← p5/replication/coefs_main_models.csv (Stata 04_run_models.do)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="10">
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A4:H4"/>
+    <mergeCell ref="A62:H62"/>
+    <mergeCell ref="A92:H92"/>
+    <mergeCell ref="A91:H91"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A63:H63"/>
+    <mergeCell ref="A36:H36"/>
+    <mergeCell ref="A5:H5"/>
+    <mergeCell ref="A37:H37"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
 </file>